--- a/2026A/心理学実験2/実験2_2_自由再生による記憶の系列位置効果/心理学実験2_実験2_系列位置効果_19名の結果_260614.xlsx
+++ b/2026A/心理学実験2/実験2_2_自由再生による記憶の系列位置効果/心理学実験2_実験2_系列位置効果_19名の結果_260614.xlsx
@@ -1,33 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s_taj\Documents\0_Works\HIJYOUKIN\放送大学\2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matsu\github\OUJ\2026A\心理学実験2\実験2_2_自由再生による記憶の系列位置効果\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCA02CD4-E19E-4DDF-AC1F-86217708DA59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BDD3506-12F9-4736-AE6E-221AF2A9F708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="13866" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1810" yWindow="2040" windowWidth="14400" windowHeight="7360" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="計算過程" sheetId="3" r:id="rId1"/>
     <sheet name="表1、2" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -394,7 +383,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -437,12 +426,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="桁区切り" xfId="1" builtinId="6"/>
@@ -459,6 +442,2423 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ja-JP"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'表1、2'!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>直後再生条件</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'表1、2'!$B$3:$P$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'表1、2'!$B$4:$P$4</c:f>
+              <c:numCache>
+                <c:formatCode>0.00_ </c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.45</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.35</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.27500000000000002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.45</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.17499999999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.22500000000000001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.17499999999999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.35</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.32500000000000001</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.375</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4691-44B1-A4C0-F2CE16CC0A86}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'表1、2'!$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>遅延再生条件</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'表1、2'!$B$3:$P$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'表1、2'!$B$5:$P$5</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>0.55555555555555558</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.30555555555555558</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.22222222222222221</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.19444444444444445</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.3888888888888889</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.1388888888888889</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.22222222222222221</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.3888888888888889</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.3888888888888889</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.3888888888888889</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.30555555555555558</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.27777777777777779</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.44444444444444442</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.33333333333333331</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-4691-44B1-A4C0-F2CE16CC0A86}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1708971664"/>
+        <c:axId val="1708972144"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1708971664"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ja-JP" altLang="en-US"/>
+                  <a:t>系列位置</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ja-JP"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1708972144"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1708972144"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ja-JP" altLang="en-US"/>
+                  <a:t>正再生率軸</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ja-JP"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.00_ " sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1708971664"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ja-JP"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ja-JP"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'表1、2'!$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>直後再生条件</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'表1、2'!$B$8:$P$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'表1、2'!$B$9:$P$9</c:f>
+              <c:numCache>
+                <c:formatCode>0.00_ </c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>2.4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.4375</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.8571428571428572</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.375</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.375</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.9444444444444446</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4.8571428571428568</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.8888888888888888</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3.6666666666666665</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4.1428571428571432</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.2222222222222223</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3.3888888888888888</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C958-464E-BE1B-4B73CDF77B62}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'表1、2'!$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>遅延再生条件</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'表1、2'!$B$8:$P$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'表1、2'!$B$10:$P$10</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.9375</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.1666666666666665</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.4285714285714284</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.166666666666667</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.6111111111111112</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.6666666666666665</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.7142857142857144</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.9285714285714284</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.2142857142857144</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4.75</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3.4285714285714284</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4.125</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3.75</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.75</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-C958-464E-BE1B-4B73CDF77B62}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1451777392"/>
+        <c:axId val="1451778352"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1451777392"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ja-JP" altLang="en-US"/>
+                  <a:t>系列位置</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ja-JP"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1451778352"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1451778352"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ja-JP" altLang="en-US"/>
+                  <a:t>再生順</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ja-JP"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.00_ " sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1451777392"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ja-JP"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>80065</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>102704</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>245717</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>234122</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="グラフ 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{183A496B-26D3-7162-F568-9E8E1051293F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>477632</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>36444</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>13806</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>167862</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="グラフ 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DCA5C6FD-DCE2-92CC-364F-05A7157A4EC0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -749,23 +3149,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q63"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>7</v>
       </c>
@@ -815,225 +3215,209 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5">
         <v>1</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="2">
         <v>4.5</v>
       </c>
-      <c r="C5" s="14">
-        <v>1</v>
-      </c>
-      <c r="D5" s="14">
+      <c r="C5" s="2">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2">
         <v>8</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="2">
         <v>4</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="2">
         <v>4.5</v>
       </c>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14">
-        <v>3</v>
-      </c>
-      <c r="I5" s="14">
+      <c r="H5" s="2">
+        <v>3</v>
+      </c>
+      <c r="I5" s="2">
         <v>4</v>
       </c>
-      <c r="J5" s="14">
-        <v>3</v>
-      </c>
-      <c r="K5" s="14">
-        <v>3</v>
-      </c>
-      <c r="L5" s="14">
+      <c r="J5" s="2">
+        <v>3</v>
+      </c>
+      <c r="K5" s="2">
+        <v>3</v>
+      </c>
+      <c r="L5" s="2">
         <v>5</v>
       </c>
-      <c r="M5" s="14">
-        <v>1</v>
-      </c>
-      <c r="N5" s="14"/>
-      <c r="O5" s="14">
+      <c r="M5" s="2">
+        <v>1</v>
+      </c>
+      <c r="O5" s="2">
         <v>1.5</v>
       </c>
-      <c r="P5" s="14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P5" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
         <v>2</v>
       </c>
-      <c r="B6" s="14">
-        <v>3</v>
-      </c>
-      <c r="C6" s="14">
+      <c r="B6" s="2">
+        <v>3</v>
+      </c>
+      <c r="C6" s="2">
         <v>4</v>
       </c>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14">
+      <c r="E6" s="2">
         <v>4</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="2">
         <v>3.5</v>
       </c>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14">
+      <c r="J6" s="2">
         <v>6</v>
       </c>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14">
+      <c r="L6" s="2">
         <v>4</v>
       </c>
-      <c r="M6" s="14">
+      <c r="M6" s="2">
         <v>5</v>
       </c>
-      <c r="N6" s="14">
-        <v>1</v>
-      </c>
-      <c r="O6" s="14">
+      <c r="N6" s="2">
+        <v>1</v>
+      </c>
+      <c r="O6" s="2">
         <v>1.5</v>
       </c>
-      <c r="P6" s="14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P6" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
         <v>3</v>
       </c>
-      <c r="B7" s="14">
-        <v>1</v>
-      </c>
-      <c r="C7" s="14">
+      <c r="B7" s="2">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2">
         <v>2.5</v>
       </c>
-      <c r="D7" s="14">
-        <v>2</v>
-      </c>
-      <c r="E7" s="14">
+      <c r="D7" s="2">
+        <v>2</v>
+      </c>
+      <c r="E7" s="2">
         <v>5.5</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="2">
         <v>5.5</v>
       </c>
-      <c r="G7" s="14">
+      <c r="G7" s="2">
         <v>4</v>
       </c>
-      <c r="H7" s="14">
+      <c r="H7" s="2">
         <v>4.5</v>
       </c>
-      <c r="I7" s="14">
+      <c r="I7" s="2">
         <v>6</v>
       </c>
-      <c r="J7" s="14">
+      <c r="J7" s="2">
         <v>5</v>
       </c>
-      <c r="K7" s="14">
+      <c r="K7" s="2">
         <v>6</v>
       </c>
-      <c r="L7" s="14">
+      <c r="L7" s="2">
         <v>8</v>
       </c>
-      <c r="M7" s="14">
+      <c r="M7" s="2">
         <v>9</v>
       </c>
-      <c r="N7" s="14">
+      <c r="N7" s="2">
         <v>5.5</v>
       </c>
-      <c r="O7" s="14">
+      <c r="O7" s="2">
         <v>4</v>
       </c>
-      <c r="P7" s="14">
+      <c r="P7" s="2">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
         <v>4</v>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="2">
         <v>4</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="2">
         <v>4</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="2">
         <v>5</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="2">
         <v>8.5</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="2">
         <v>6.5</v>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="2">
         <v>4</v>
       </c>
-      <c r="H8" s="14">
+      <c r="H8" s="2">
         <v>4</v>
       </c>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14">
+      <c r="J8" s="2">
         <v>5</v>
       </c>
-      <c r="K8" s="14">
+      <c r="K8" s="2">
         <v>7</v>
       </c>
-      <c r="L8" s="14">
-        <v>1</v>
-      </c>
-      <c r="M8" s="14">
-        <v>2</v>
-      </c>
-      <c r="N8" s="14">
+      <c r="L8" s="2">
+        <v>1</v>
+      </c>
+      <c r="M8" s="2">
+        <v>2</v>
+      </c>
+      <c r="N8" s="2">
         <v>4.5</v>
       </c>
-      <c r="O8" s="14">
+      <c r="O8" s="2">
         <v>1.5</v>
       </c>
-      <c r="P8" s="14">
+      <c r="P8" s="2">
         <v>2.5</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
         <v>5</v>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="2">
         <v>2.5</v>
       </c>
-      <c r="C9" s="14">
-        <v>2</v>
-      </c>
-      <c r="D9" s="14">
-        <v>3</v>
-      </c>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="14"/>
-      <c r="L9" s="14">
-        <v>2</v>
-      </c>
-      <c r="M9" s="14">
-        <v>2</v>
-      </c>
-      <c r="N9" s="14">
+      <c r="C9" s="2">
+        <v>2</v>
+      </c>
+      <c r="D9" s="2">
+        <v>3</v>
+      </c>
+      <c r="L9" s="2">
+        <v>2</v>
+      </c>
+      <c r="M9" s="2">
+        <v>2</v>
+      </c>
+      <c r="N9" s="2">
         <v>2.5</v>
       </c>
-      <c r="O9" s="14">
-        <v>1</v>
-      </c>
-      <c r="P9" s="14"/>
-    </row>
-    <row r="10" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O9" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
         <v>6</v>
       </c>
@@ -1071,7 +3455,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
         <v>7</v>
       </c>
@@ -1100,7 +3484,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
         <v>8</v>
       </c>
@@ -1147,7 +3531,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="5">
         <v>9</v>
       </c>
@@ -1176,7 +3560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
         <v>10</v>
       </c>
@@ -1214,7 +3598,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>2</v>
       </c>
@@ -1227,7 +3611,7 @@
         <v>2.4375</v>
       </c>
       <c r="D15" s="4">
-        <f t="shared" ref="C15:P15" si="0">AVERAGE(D5:D14)</f>
+        <f t="shared" ref="D15:P15" si="0">AVERAGE(D5:D14)</f>
         <v>3.8571428571428572</v>
       </c>
       <c r="E15" s="4">
@@ -1279,7 +3663,7 @@
         <v>3.3888888888888888</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>3</v>
       </c>
@@ -1292,7 +3676,7 @@
         <v>1.0500850305706539</v>
       </c>
       <c r="D16" s="4">
-        <f t="shared" ref="C16:P16" si="1">STDEV(D5:D14)</f>
+        <f t="shared" ref="D16:P16" si="1">STDEV(D5:D14)</f>
         <v>2.0354009783964297</v>
       </c>
       <c r="E16" s="4">
@@ -1344,12 +3728,12 @@
         <v>2.0883273476902779</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>7</v>
       </c>
@@ -1399,223 +3783,206 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="5">
         <v>1</v>
       </c>
-      <c r="B20" s="14">
+      <c r="B20" s="2">
         <v>4.5</v>
       </c>
-      <c r="C20" s="14">
-        <v>2</v>
-      </c>
-      <c r="D20" s="14">
-        <v>1</v>
-      </c>
-      <c r="E20" s="14">
+      <c r="C20" s="2">
+        <v>2</v>
+      </c>
+      <c r="D20" s="2">
+        <v>1</v>
+      </c>
+      <c r="E20" s="2">
         <v>4</v>
       </c>
-      <c r="F20" s="14">
-        <v>3</v>
-      </c>
-      <c r="G20" s="14">
-        <v>3</v>
-      </c>
-      <c r="H20" s="14"/>
-      <c r="I20" s="14"/>
-      <c r="J20" s="14">
+      <c r="F20" s="2">
+        <v>3</v>
+      </c>
+      <c r="G20" s="2">
+        <v>3</v>
+      </c>
+      <c r="J20" s="2">
         <v>4</v>
       </c>
-      <c r="K20" s="14"/>
-      <c r="L20" s="14"/>
-      <c r="M20" s="14">
+      <c r="M20" s="2">
         <v>2.5</v>
       </c>
-      <c r="N20" s="14">
-        <v>1</v>
-      </c>
-      <c r="O20" s="14">
+      <c r="N20" s="2">
+        <v>1</v>
+      </c>
+      <c r="O20" s="2">
         <v>5</v>
       </c>
-      <c r="P20" s="14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P20" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="5">
         <v>2</v>
       </c>
-      <c r="B21" s="14">
-        <v>1</v>
-      </c>
-      <c r="C21" s="14">
-        <v>3</v>
-      </c>
-      <c r="D21" s="14">
+      <c r="B21" s="2">
+        <v>1</v>
+      </c>
+      <c r="C21" s="2">
+        <v>3</v>
+      </c>
+      <c r="D21" s="2">
         <v>5</v>
       </c>
-      <c r="E21" s="14">
+      <c r="E21" s="2">
         <v>4</v>
       </c>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14">
-        <v>3</v>
-      </c>
-      <c r="H21" s="14"/>
-      <c r="I21" s="14">
-        <v>1</v>
-      </c>
-      <c r="J21" s="14">
-        <v>2</v>
-      </c>
-      <c r="K21" s="14"/>
-      <c r="L21" s="14">
+      <c r="G21" s="2">
+        <v>3</v>
+      </c>
+      <c r="I21" s="2">
+        <v>1</v>
+      </c>
+      <c r="J21" s="2">
+        <v>2</v>
+      </c>
+      <c r="L21" s="2">
         <v>5</v>
       </c>
-      <c r="M21" s="14">
-        <v>2</v>
-      </c>
-      <c r="N21" s="14"/>
-      <c r="O21" s="14">
+      <c r="M21" s="2">
+        <v>2</v>
+      </c>
+      <c r="O21" s="2">
         <v>4</v>
       </c>
-      <c r="P21" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P21" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="5">
         <v>3</v>
       </c>
-      <c r="B22" s="14">
-        <v>1</v>
-      </c>
-      <c r="C22" s="14">
+      <c r="B22" s="2">
+        <v>1</v>
+      </c>
+      <c r="C22" s="2">
         <v>4</v>
       </c>
-      <c r="D22" s="14">
-        <v>3</v>
-      </c>
-      <c r="E22" s="14">
-        <v>2</v>
-      </c>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14">
+      <c r="D22" s="2">
+        <v>3</v>
+      </c>
+      <c r="E22" s="2">
+        <v>2</v>
+      </c>
+      <c r="G22" s="2">
         <v>5</v>
       </c>
-      <c r="H22" s="14"/>
-      <c r="I22" s="14">
+      <c r="I22" s="2">
         <v>4</v>
       </c>
-      <c r="J22" s="14">
+      <c r="J22" s="2">
         <v>7</v>
       </c>
-      <c r="K22" s="14">
-        <v>3</v>
-      </c>
-      <c r="L22" s="14">
+      <c r="K22" s="2">
+        <v>3</v>
+      </c>
+      <c r="L22" s="2">
         <v>5</v>
       </c>
-      <c r="M22" s="14">
-        <v>1</v>
-      </c>
-      <c r="N22" s="14">
+      <c r="M22" s="2">
+        <v>1</v>
+      </c>
+      <c r="N22" s="2">
         <v>4</v>
       </c>
-      <c r="O22" s="14">
+      <c r="O22" s="2">
         <v>2.5</v>
       </c>
-      <c r="P22" s="14">
+      <c r="P22" s="2">
         <v>2.5</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="5">
         <v>4</v>
       </c>
-      <c r="B23" s="14">
-        <v>1</v>
-      </c>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14">
-        <v>2</v>
-      </c>
-      <c r="G23" s="14">
+      <c r="B23" s="2">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>2</v>
+      </c>
+      <c r="G23" s="2">
         <v>2.5</v>
       </c>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="14"/>
-      <c r="K23" s="14">
+      <c r="K23" s="2">
         <v>4.5</v>
       </c>
-      <c r="L23" s="14">
+      <c r="L23" s="2">
         <v>4.5</v>
       </c>
-      <c r="M23" s="14"/>
-      <c r="N23" s="14">
+      <c r="N23" s="2">
         <v>4</v>
       </c>
-      <c r="O23" s="14">
+      <c r="O23" s="2">
         <v>4</v>
       </c>
-      <c r="P23" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P23" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="5">
         <v>5</v>
       </c>
-      <c r="B24" s="15">
+      <c r="B24" s="2">
         <v>4.5</v>
       </c>
-      <c r="C24" s="15">
+      <c r="C24" s="2">
         <v>7</v>
       </c>
-      <c r="D24" s="15">
-        <v>1</v>
-      </c>
-      <c r="E24" s="15">
+      <c r="D24" s="2">
+        <v>1</v>
+      </c>
+      <c r="E24" s="2">
         <v>7</v>
       </c>
-      <c r="F24" s="15">
+      <c r="F24" s="2">
         <v>8</v>
       </c>
-      <c r="G24" s="15">
+      <c r="G24" s="2">
         <v>4</v>
       </c>
-      <c r="H24" s="15">
-        <v>1</v>
-      </c>
-      <c r="I24" s="15">
-        <v>2</v>
-      </c>
-      <c r="J24" s="15">
-        <v>3</v>
-      </c>
-      <c r="K24" s="15">
+      <c r="H24" s="2">
+        <v>1</v>
+      </c>
+      <c r="I24" s="2">
+        <v>2</v>
+      </c>
+      <c r="J24" s="2">
+        <v>3</v>
+      </c>
+      <c r="K24" s="2">
         <v>5</v>
       </c>
-      <c r="L24" s="15">
+      <c r="L24" s="2">
         <v>5</v>
       </c>
-      <c r="M24" s="15">
-        <v>3</v>
-      </c>
-      <c r="N24" s="15">
+      <c r="M24" s="2">
+        <v>3</v>
+      </c>
+      <c r="N24" s="2">
         <v>6</v>
       </c>
-      <c r="O24" s="15">
+      <c r="O24" s="2">
         <v>5</v>
       </c>
-      <c r="P24" s="15">
+      <c r="P24" s="2">
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="5">
         <v>6</v>
       </c>
@@ -1662,7 +4029,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="5">
         <v>7</v>
       </c>
@@ -1700,7 +4067,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="5">
         <v>8</v>
       </c>
@@ -1738,7 +4105,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="5">
         <v>9</v>
       </c>
@@ -1773,7 +4140,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>2</v>
       </c>
@@ -1838,7 +4205,7 @@
         <v>2.75</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>3</v>
       </c>
@@ -1903,17 +4270,17 @@
         <v>1.8371173070873836</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
         <v>7</v>
       </c>
@@ -1963,307 +4330,307 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="5">
         <v>1</v>
       </c>
-      <c r="B36" s="14">
+      <c r="B36" s="2">
         <v>4</v>
       </c>
-      <c r="C36" s="14">
-        <v>1</v>
-      </c>
-      <c r="D36" s="14">
-        <v>1</v>
-      </c>
-      <c r="E36" s="14">
-        <v>3</v>
-      </c>
-      <c r="F36" s="14">
-        <v>2</v>
-      </c>
-      <c r="G36" s="14">
-        <v>0</v>
-      </c>
-      <c r="H36" s="14">
-        <v>1</v>
-      </c>
-      <c r="I36" s="14">
-        <v>1</v>
-      </c>
-      <c r="J36" s="14">
-        <v>2</v>
-      </c>
-      <c r="K36" s="14">
-        <v>1</v>
-      </c>
-      <c r="L36" s="14">
-        <v>1</v>
-      </c>
-      <c r="M36" s="14">
-        <v>1</v>
-      </c>
-      <c r="N36" s="14">
-        <v>0</v>
-      </c>
-      <c r="O36" s="14">
-        <v>2</v>
-      </c>
-      <c r="P36" s="14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C36" s="2">
+        <v>1</v>
+      </c>
+      <c r="D36" s="2">
+        <v>1</v>
+      </c>
+      <c r="E36" s="2">
+        <v>3</v>
+      </c>
+      <c r="F36" s="2">
+        <v>2</v>
+      </c>
+      <c r="G36" s="2">
+        <v>0</v>
+      </c>
+      <c r="H36" s="2">
+        <v>1</v>
+      </c>
+      <c r="I36" s="2">
+        <v>1</v>
+      </c>
+      <c r="J36" s="2">
+        <v>2</v>
+      </c>
+      <c r="K36" s="2">
+        <v>1</v>
+      </c>
+      <c r="L36" s="2">
+        <v>1</v>
+      </c>
+      <c r="M36" s="2">
+        <v>1</v>
+      </c>
+      <c r="N36" s="2">
+        <v>0</v>
+      </c>
+      <c r="O36" s="2">
+        <v>2</v>
+      </c>
+      <c r="P36" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="5">
         <v>2</v>
       </c>
-      <c r="B37" s="14">
-        <v>1</v>
-      </c>
-      <c r="C37" s="14">
-        <v>3</v>
-      </c>
-      <c r="D37" s="14">
-        <v>0</v>
-      </c>
-      <c r="E37" s="14">
-        <v>1</v>
-      </c>
-      <c r="F37" s="14">
-        <v>2</v>
-      </c>
-      <c r="G37" s="14">
-        <v>0</v>
-      </c>
-      <c r="H37" s="14">
-        <v>0</v>
-      </c>
-      <c r="I37" s="14">
-        <v>0</v>
-      </c>
-      <c r="J37" s="14">
-        <v>1</v>
-      </c>
-      <c r="K37" s="14">
-        <v>0</v>
-      </c>
-      <c r="L37" s="14">
-        <v>2</v>
-      </c>
-      <c r="M37" s="14">
-        <v>1</v>
-      </c>
-      <c r="N37" s="14">
-        <v>3</v>
-      </c>
-      <c r="O37" s="14">
-        <v>2</v>
-      </c>
-      <c r="P37" s="14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="2">
+        <v>1</v>
+      </c>
+      <c r="C37" s="2">
+        <v>3</v>
+      </c>
+      <c r="D37" s="2">
+        <v>0</v>
+      </c>
+      <c r="E37" s="2">
+        <v>1</v>
+      </c>
+      <c r="F37" s="2">
+        <v>2</v>
+      </c>
+      <c r="G37" s="2">
+        <v>0</v>
+      </c>
+      <c r="H37" s="2">
+        <v>0</v>
+      </c>
+      <c r="I37" s="2">
+        <v>0</v>
+      </c>
+      <c r="J37" s="2">
+        <v>1</v>
+      </c>
+      <c r="K37" s="2">
+        <v>0</v>
+      </c>
+      <c r="L37" s="2">
+        <v>2</v>
+      </c>
+      <c r="M37" s="2">
+        <v>1</v>
+      </c>
+      <c r="N37" s="2">
+        <v>3</v>
+      </c>
+      <c r="O37" s="2">
+        <v>2</v>
+      </c>
+      <c r="P37" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="5">
         <v>3</v>
       </c>
-      <c r="B38" s="14">
+      <c r="B38" s="2">
         <v>4</v>
       </c>
-      <c r="C38" s="14">
-        <v>2</v>
-      </c>
-      <c r="D38" s="14">
-        <v>2</v>
-      </c>
-      <c r="E38" s="14">
-        <v>2</v>
-      </c>
-      <c r="F38" s="14">
-        <v>2</v>
-      </c>
-      <c r="G38" s="14">
-        <v>1</v>
-      </c>
-      <c r="H38" s="14">
+      <c r="C38" s="2">
+        <v>2</v>
+      </c>
+      <c r="D38" s="2">
+        <v>2</v>
+      </c>
+      <c r="E38" s="2">
+        <v>2</v>
+      </c>
+      <c r="F38" s="2">
+        <v>2</v>
+      </c>
+      <c r="G38" s="2">
+        <v>1</v>
+      </c>
+      <c r="H38" s="2">
         <v>4</v>
       </c>
-      <c r="I38" s="14">
-        <v>2</v>
-      </c>
-      <c r="J38" s="14">
-        <v>3</v>
-      </c>
-      <c r="K38" s="14">
-        <v>2</v>
-      </c>
-      <c r="L38" s="14">
-        <v>3</v>
-      </c>
-      <c r="M38" s="14">
-        <v>1</v>
-      </c>
-      <c r="N38" s="14">
-        <v>2</v>
-      </c>
-      <c r="O38" s="14">
-        <v>1</v>
-      </c>
-      <c r="P38" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I38" s="2">
+        <v>2</v>
+      </c>
+      <c r="J38" s="2">
+        <v>3</v>
+      </c>
+      <c r="K38" s="2">
+        <v>2</v>
+      </c>
+      <c r="L38" s="2">
+        <v>3</v>
+      </c>
+      <c r="M38" s="2">
+        <v>1</v>
+      </c>
+      <c r="N38" s="2">
+        <v>2</v>
+      </c>
+      <c r="O38" s="2">
+        <v>1</v>
+      </c>
+      <c r="P38" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="5">
         <v>4</v>
       </c>
-      <c r="B39" s="14">
+      <c r="B39" s="2">
         <v>4</v>
       </c>
-      <c r="C39" s="14">
-        <v>3</v>
-      </c>
-      <c r="D39" s="14">
-        <v>2</v>
-      </c>
-      <c r="E39" s="14">
-        <v>2</v>
-      </c>
-      <c r="F39" s="14">
-        <v>2</v>
-      </c>
-      <c r="G39" s="14">
-        <v>1</v>
-      </c>
-      <c r="H39" s="14">
-        <v>2</v>
-      </c>
-      <c r="I39" s="14">
-        <v>0</v>
-      </c>
-      <c r="J39" s="14">
-        <v>3</v>
-      </c>
-      <c r="K39" s="14">
-        <v>1</v>
-      </c>
-      <c r="L39" s="14">
-        <v>1</v>
-      </c>
-      <c r="M39" s="14">
-        <v>3</v>
-      </c>
-      <c r="N39" s="14">
-        <v>2</v>
-      </c>
-      <c r="O39" s="14">
-        <v>2</v>
-      </c>
-      <c r="P39" s="14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C39" s="2">
+        <v>3</v>
+      </c>
+      <c r="D39" s="2">
+        <v>2</v>
+      </c>
+      <c r="E39" s="2">
+        <v>2</v>
+      </c>
+      <c r="F39" s="2">
+        <v>2</v>
+      </c>
+      <c r="G39" s="2">
+        <v>1</v>
+      </c>
+      <c r="H39" s="2">
+        <v>2</v>
+      </c>
+      <c r="I39" s="2">
+        <v>0</v>
+      </c>
+      <c r="J39" s="2">
+        <v>3</v>
+      </c>
+      <c r="K39" s="2">
+        <v>1</v>
+      </c>
+      <c r="L39" s="2">
+        <v>1</v>
+      </c>
+      <c r="M39" s="2">
+        <v>3</v>
+      </c>
+      <c r="N39" s="2">
+        <v>2</v>
+      </c>
+      <c r="O39" s="2">
+        <v>2</v>
+      </c>
+      <c r="P39" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="5">
         <v>5</v>
       </c>
-      <c r="B40" s="14">
-        <v>2</v>
-      </c>
-      <c r="C40" s="14">
-        <v>1</v>
-      </c>
-      <c r="D40" s="14">
-        <v>1</v>
-      </c>
-      <c r="E40" s="14">
-        <v>0</v>
-      </c>
-      <c r="F40" s="14">
-        <v>0</v>
-      </c>
-      <c r="G40" s="14">
-        <v>0</v>
-      </c>
-      <c r="H40" s="14">
-        <v>0</v>
-      </c>
-      <c r="I40" s="14">
-        <v>0</v>
-      </c>
-      <c r="J40" s="14">
-        <v>0</v>
-      </c>
-      <c r="K40" s="14">
-        <v>0</v>
-      </c>
-      <c r="L40" s="14">
-        <v>2</v>
-      </c>
-      <c r="M40" s="14">
-        <v>2</v>
-      </c>
-      <c r="N40" s="14">
-        <v>2</v>
-      </c>
-      <c r="O40" s="14">
-        <v>1</v>
-      </c>
-      <c r="P40" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="2">
+        <v>2</v>
+      </c>
+      <c r="C40" s="2">
+        <v>1</v>
+      </c>
+      <c r="D40" s="2">
+        <v>1</v>
+      </c>
+      <c r="E40" s="2">
+        <v>0</v>
+      </c>
+      <c r="F40" s="2">
+        <v>0</v>
+      </c>
+      <c r="G40" s="2">
+        <v>0</v>
+      </c>
+      <c r="H40" s="2">
+        <v>0</v>
+      </c>
+      <c r="I40" s="2">
+        <v>0</v>
+      </c>
+      <c r="J40" s="2">
+        <v>0</v>
+      </c>
+      <c r="K40" s="2">
+        <v>0</v>
+      </c>
+      <c r="L40" s="2">
+        <v>2</v>
+      </c>
+      <c r="M40" s="2">
+        <v>2</v>
+      </c>
+      <c r="N40" s="2">
+        <v>2</v>
+      </c>
+      <c r="O40" s="2">
+        <v>1</v>
+      </c>
+      <c r="P40" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="5">
         <v>6</v>
       </c>
-      <c r="B41" s="15">
-        <v>1</v>
-      </c>
-      <c r="C41" s="15">
-        <v>2</v>
-      </c>
-      <c r="D41" s="15">
-        <v>2</v>
-      </c>
-      <c r="E41" s="15">
-        <v>0</v>
-      </c>
-      <c r="F41" s="15">
-        <v>2</v>
-      </c>
-      <c r="G41" s="15">
-        <v>1</v>
-      </c>
-      <c r="H41" s="15">
-        <v>0</v>
-      </c>
-      <c r="I41" s="15">
-        <v>0</v>
-      </c>
-      <c r="J41" s="15">
-        <v>1</v>
-      </c>
-      <c r="K41" s="15">
-        <v>0</v>
-      </c>
-      <c r="L41" s="15">
-        <v>1</v>
-      </c>
-      <c r="M41" s="15">
-        <v>1</v>
-      </c>
-      <c r="N41" s="15">
-        <v>1</v>
-      </c>
-      <c r="O41" s="15">
-        <v>2</v>
-      </c>
-      <c r="P41" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="2">
+        <v>1</v>
+      </c>
+      <c r="C41" s="2">
+        <v>2</v>
+      </c>
+      <c r="D41" s="2">
+        <v>2</v>
+      </c>
+      <c r="E41" s="2">
+        <v>0</v>
+      </c>
+      <c r="F41" s="2">
+        <v>2</v>
+      </c>
+      <c r="G41" s="2">
+        <v>1</v>
+      </c>
+      <c r="H41" s="2">
+        <v>0</v>
+      </c>
+      <c r="I41" s="2">
+        <v>0</v>
+      </c>
+      <c r="J41" s="2">
+        <v>1</v>
+      </c>
+      <c r="K41" s="2">
+        <v>0</v>
+      </c>
+      <c r="L41" s="2">
+        <v>1</v>
+      </c>
+      <c r="M41" s="2">
+        <v>1</v>
+      </c>
+      <c r="N41" s="2">
+        <v>1</v>
+      </c>
+      <c r="O41" s="2">
+        <v>2</v>
+      </c>
+      <c r="P41" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="5">
         <v>7</v>
       </c>
@@ -2313,7 +4680,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="5">
         <v>8</v>
       </c>
@@ -2363,7 +4730,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="5">
         <v>9</v>
       </c>
@@ -2413,7 +4780,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="5">
         <v>10</v>
       </c>
@@ -2463,7 +4830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>4</v>
       </c>
@@ -2528,7 +4895,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>5</v>
       </c>
@@ -2593,7 +4960,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>3</v>
       </c>
@@ -2658,12 +5025,12 @@
         <v>1.247219128924647</v>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
         <v>7</v>
       </c>
@@ -2713,307 +5080,307 @@
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="5">
         <v>1</v>
       </c>
-      <c r="B52" s="14">
-        <v>2</v>
-      </c>
-      <c r="C52" s="14">
-        <v>1</v>
-      </c>
-      <c r="D52" s="14">
-        <v>1</v>
-      </c>
-      <c r="E52" s="14">
-        <v>2</v>
-      </c>
-      <c r="F52" s="14">
-        <v>1</v>
-      </c>
-      <c r="G52" s="14">
-        <v>2</v>
-      </c>
-      <c r="H52" s="14">
-        <v>0</v>
-      </c>
-      <c r="I52" s="14">
-        <v>0</v>
-      </c>
-      <c r="J52" s="14">
-        <v>3</v>
-      </c>
-      <c r="K52" s="14">
-        <v>0</v>
-      </c>
-      <c r="L52" s="14">
-        <v>0</v>
-      </c>
-      <c r="M52" s="14">
-        <v>2</v>
-      </c>
-      <c r="N52" s="14">
-        <v>1</v>
-      </c>
-      <c r="O52" s="14">
-        <v>2</v>
-      </c>
-      <c r="P52" s="14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B52" s="2">
+        <v>2</v>
+      </c>
+      <c r="C52" s="2">
+        <v>1</v>
+      </c>
+      <c r="D52" s="2">
+        <v>1</v>
+      </c>
+      <c r="E52" s="2">
+        <v>2</v>
+      </c>
+      <c r="F52" s="2">
+        <v>1</v>
+      </c>
+      <c r="G52" s="2">
+        <v>2</v>
+      </c>
+      <c r="H52" s="2">
+        <v>0</v>
+      </c>
+      <c r="I52" s="2">
+        <v>0</v>
+      </c>
+      <c r="J52" s="2">
+        <v>3</v>
+      </c>
+      <c r="K52" s="2">
+        <v>0</v>
+      </c>
+      <c r="L52" s="2">
+        <v>0</v>
+      </c>
+      <c r="M52" s="2">
+        <v>2</v>
+      </c>
+      <c r="N52" s="2">
+        <v>1</v>
+      </c>
+      <c r="O52" s="2">
+        <v>2</v>
+      </c>
+      <c r="P52" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="5">
         <v>2</v>
       </c>
-      <c r="B53" s="14">
-        <v>1</v>
-      </c>
-      <c r="C53" s="14">
-        <v>1</v>
-      </c>
-      <c r="D53" s="14">
-        <v>1</v>
-      </c>
-      <c r="E53" s="14">
-        <v>1</v>
-      </c>
-      <c r="F53" s="14">
-        <v>0</v>
-      </c>
-      <c r="G53" s="14">
-        <v>2</v>
-      </c>
-      <c r="H53" s="14">
-        <v>0</v>
-      </c>
-      <c r="I53" s="14">
-        <v>1</v>
-      </c>
-      <c r="J53" s="14">
-        <v>3</v>
-      </c>
-      <c r="K53" s="14">
-        <v>0</v>
-      </c>
-      <c r="L53" s="14">
-        <v>1</v>
-      </c>
-      <c r="M53" s="14">
-        <v>1</v>
-      </c>
-      <c r="N53" s="14">
-        <v>0</v>
-      </c>
-      <c r="O53" s="14">
-        <v>1</v>
-      </c>
-      <c r="P53" s="14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="54" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B53" s="2">
+        <v>1</v>
+      </c>
+      <c r="C53" s="2">
+        <v>1</v>
+      </c>
+      <c r="D53" s="2">
+        <v>1</v>
+      </c>
+      <c r="E53" s="2">
+        <v>1</v>
+      </c>
+      <c r="F53" s="2">
+        <v>0</v>
+      </c>
+      <c r="G53" s="2">
+        <v>2</v>
+      </c>
+      <c r="H53" s="2">
+        <v>0</v>
+      </c>
+      <c r="I53" s="2">
+        <v>1</v>
+      </c>
+      <c r="J53" s="2">
+        <v>3</v>
+      </c>
+      <c r="K53" s="2">
+        <v>0</v>
+      </c>
+      <c r="L53" s="2">
+        <v>1</v>
+      </c>
+      <c r="M53" s="2">
+        <v>1</v>
+      </c>
+      <c r="N53" s="2">
+        <v>0</v>
+      </c>
+      <c r="O53" s="2">
+        <v>1</v>
+      </c>
+      <c r="P53" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="5">
         <v>3</v>
       </c>
-      <c r="B54" s="14">
-        <v>1</v>
-      </c>
-      <c r="C54" s="14">
-        <v>1</v>
-      </c>
-      <c r="D54" s="14">
-        <v>2</v>
-      </c>
-      <c r="E54" s="14">
-        <v>1</v>
-      </c>
-      <c r="F54" s="14">
-        <v>0</v>
-      </c>
-      <c r="G54" s="14">
-        <v>1</v>
-      </c>
-      <c r="H54" s="14">
-        <v>0</v>
-      </c>
-      <c r="I54" s="14">
-        <v>1</v>
-      </c>
-      <c r="J54" s="14">
-        <v>1</v>
-      </c>
-      <c r="K54" s="14">
-        <v>1</v>
-      </c>
-      <c r="L54" s="14">
+      <c r="B54" s="2">
+        <v>1</v>
+      </c>
+      <c r="C54" s="2">
+        <v>1</v>
+      </c>
+      <c r="D54" s="2">
+        <v>2</v>
+      </c>
+      <c r="E54" s="2">
+        <v>1</v>
+      </c>
+      <c r="F54" s="2">
+        <v>0</v>
+      </c>
+      <c r="G54" s="2">
+        <v>1</v>
+      </c>
+      <c r="H54" s="2">
+        <v>0</v>
+      </c>
+      <c r="I54" s="2">
+        <v>1</v>
+      </c>
+      <c r="J54" s="2">
+        <v>1</v>
+      </c>
+      <c r="K54" s="2">
+        <v>1</v>
+      </c>
+      <c r="L54" s="2">
         <v>4</v>
       </c>
-      <c r="M54" s="14">
-        <v>1</v>
-      </c>
-      <c r="N54" s="14">
-        <v>1</v>
-      </c>
-      <c r="O54" s="14">
+      <c r="M54" s="2">
+        <v>1</v>
+      </c>
+      <c r="N54" s="2">
+        <v>1</v>
+      </c>
+      <c r="O54" s="2">
         <v>4</v>
       </c>
-      <c r="P54" s="14">
+      <c r="P54" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="5">
         <v>4</v>
       </c>
-      <c r="B55" s="14">
-        <v>3</v>
-      </c>
-      <c r="C55" s="14">
-        <v>0</v>
-      </c>
-      <c r="D55" s="14">
-        <v>0</v>
-      </c>
-      <c r="E55" s="14">
-        <v>0</v>
-      </c>
-      <c r="F55" s="14">
-        <v>1</v>
-      </c>
-      <c r="G55" s="14">
-        <v>2</v>
-      </c>
-      <c r="H55" s="14">
-        <v>0</v>
-      </c>
-      <c r="I55" s="14">
-        <v>0</v>
-      </c>
-      <c r="J55" s="14">
-        <v>0</v>
-      </c>
-      <c r="K55" s="14">
-        <v>2</v>
-      </c>
-      <c r="L55" s="14">
+      <c r="B55" s="2">
+        <v>3</v>
+      </c>
+      <c r="C55" s="2">
+        <v>0</v>
+      </c>
+      <c r="D55" s="2">
+        <v>0</v>
+      </c>
+      <c r="E55" s="2">
+        <v>0</v>
+      </c>
+      <c r="F55" s="2">
+        <v>1</v>
+      </c>
+      <c r="G55" s="2">
+        <v>2</v>
+      </c>
+      <c r="H55" s="2">
+        <v>0</v>
+      </c>
+      <c r="I55" s="2">
+        <v>0</v>
+      </c>
+      <c r="J55" s="2">
+        <v>0</v>
+      </c>
+      <c r="K55" s="2">
+        <v>2</v>
+      </c>
+      <c r="L55" s="2">
         <v>4</v>
       </c>
-      <c r="M55" s="14">
-        <v>0</v>
-      </c>
-      <c r="N55" s="14">
-        <v>2</v>
-      </c>
-      <c r="O55" s="14">
-        <v>1</v>
-      </c>
-      <c r="P55" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M55" s="2">
+        <v>0</v>
+      </c>
+      <c r="N55" s="2">
+        <v>2</v>
+      </c>
+      <c r="O55" s="2">
+        <v>1</v>
+      </c>
+      <c r="P55" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="5">
         <v>5</v>
       </c>
-      <c r="B56" s="15">
+      <c r="B56" s="2">
         <v>4</v>
       </c>
-      <c r="C56" s="15">
-        <v>1</v>
-      </c>
-      <c r="D56" s="15">
-        <v>1</v>
-      </c>
-      <c r="E56" s="15">
-        <v>1</v>
-      </c>
-      <c r="F56" s="15">
-        <v>1</v>
-      </c>
-      <c r="G56" s="15">
-        <v>1</v>
-      </c>
-      <c r="H56" s="15">
-        <v>3</v>
-      </c>
-      <c r="I56" s="15">
-        <v>1</v>
-      </c>
-      <c r="J56" s="15">
-        <v>1</v>
-      </c>
-      <c r="K56" s="15">
-        <v>2</v>
-      </c>
-      <c r="L56" s="15">
-        <v>2</v>
-      </c>
-      <c r="M56" s="15">
-        <v>3</v>
-      </c>
-      <c r="N56" s="15">
-        <v>2</v>
-      </c>
-      <c r="O56" s="15">
-        <v>3</v>
-      </c>
-      <c r="P56" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C56" s="2">
+        <v>1</v>
+      </c>
+      <c r="D56" s="2">
+        <v>1</v>
+      </c>
+      <c r="E56" s="2">
+        <v>1</v>
+      </c>
+      <c r="F56" s="2">
+        <v>1</v>
+      </c>
+      <c r="G56" s="2">
+        <v>1</v>
+      </c>
+      <c r="H56" s="2">
+        <v>3</v>
+      </c>
+      <c r="I56" s="2">
+        <v>1</v>
+      </c>
+      <c r="J56" s="2">
+        <v>1</v>
+      </c>
+      <c r="K56" s="2">
+        <v>2</v>
+      </c>
+      <c r="L56" s="2">
+        <v>2</v>
+      </c>
+      <c r="M56" s="2">
+        <v>3</v>
+      </c>
+      <c r="N56" s="2">
+        <v>2</v>
+      </c>
+      <c r="O56" s="2">
+        <v>3</v>
+      </c>
+      <c r="P56" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="5">
         <v>6</v>
       </c>
-      <c r="B57" s="15">
-        <v>2</v>
-      </c>
-      <c r="C57" s="15">
-        <v>1</v>
-      </c>
-      <c r="D57" s="15">
-        <v>0</v>
-      </c>
-      <c r="E57" s="15">
-        <v>1</v>
-      </c>
-      <c r="F57" s="15">
-        <v>1</v>
-      </c>
-      <c r="G57" s="15">
-        <v>1</v>
-      </c>
-      <c r="H57" s="15">
-        <v>1</v>
-      </c>
-      <c r="I57" s="15">
-        <v>2</v>
-      </c>
-      <c r="J57" s="15">
-        <v>2</v>
-      </c>
-      <c r="K57" s="15">
-        <v>1</v>
-      </c>
-      <c r="L57" s="15">
-        <v>1</v>
-      </c>
-      <c r="M57" s="15">
-        <v>2</v>
-      </c>
-      <c r="N57" s="15">
-        <v>1</v>
-      </c>
-      <c r="O57" s="15">
-        <v>2</v>
-      </c>
-      <c r="P57" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B57" s="2">
+        <v>2</v>
+      </c>
+      <c r="C57" s="2">
+        <v>1</v>
+      </c>
+      <c r="D57" s="2">
+        <v>0</v>
+      </c>
+      <c r="E57" s="2">
+        <v>1</v>
+      </c>
+      <c r="F57" s="2">
+        <v>1</v>
+      </c>
+      <c r="G57" s="2">
+        <v>1</v>
+      </c>
+      <c r="H57" s="2">
+        <v>1</v>
+      </c>
+      <c r="I57" s="2">
+        <v>2</v>
+      </c>
+      <c r="J57" s="2">
+        <v>2</v>
+      </c>
+      <c r="K57" s="2">
+        <v>1</v>
+      </c>
+      <c r="L57" s="2">
+        <v>1</v>
+      </c>
+      <c r="M57" s="2">
+        <v>2</v>
+      </c>
+      <c r="N57" s="2">
+        <v>1</v>
+      </c>
+      <c r="O57" s="2">
+        <v>2</v>
+      </c>
+      <c r="P57" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="5">
         <v>7</v>
       </c>
@@ -3063,7 +5430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="5">
         <v>8</v>
       </c>
@@ -3113,7 +5480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="5">
         <v>9</v>
       </c>
@@ -3163,7 +5530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
         <v>6</v>
       </c>
@@ -3229,7 +5596,7 @@
       </c>
       <c r="Q61" s="4"/>
     </row>
-    <row r="62" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
         <v>5</v>
       </c>
@@ -3294,7 +5661,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
         <v>3</v>
       </c>
@@ -3370,13 +5737,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:U13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.87890625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="7" t="s">
         <v>17</v>
       </c>
@@ -3385,7 +5752,7 @@
       <c r="T2" s="2"/>
       <c r="U2" s="2"/>
     </row>
-    <row r="3" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="8"/>
       <c r="B3" s="8">
         <v>1</v>
@@ -3442,7 +5809,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
         <v>10</v>
       </c>
@@ -3504,7 +5871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>11</v>
       </c>
@@ -3566,12 +5933,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="S6" s="2"/>
       <c r="T6" s="2"/>
       <c r="U6" s="2"/>
     </row>
-    <row r="7" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="7" t="s">
         <v>18</v>
       </c>
@@ -3579,7 +5946,7 @@
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
     </row>
-    <row r="8" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="8"/>
       <c r="B8" s="8">
         <v>1</v>
@@ -3634,7 +6001,7 @@
       </c>
       <c r="U8" s="2"/>
     </row>
-    <row r="9" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
         <v>10</v>
       </c>
@@ -3694,7 +6061,7 @@
       </c>
       <c r="U9" s="2"/>
     </row>
-    <row r="10" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
         <v>11</v>
       </c>
@@ -3754,7 +6121,7 @@
       </c>
       <c r="U10" s="2"/>
     </row>
-    <row r="11" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="R11" t="s">
         <v>19</v>
       </c>
@@ -3766,12 +6133,13 @@
       </c>
       <c r="U11" s="2"/>
     </row>
-    <row r="13" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>